--- a/Сборочные отчёты/Сборочный отчёт_2025-06-14.xlsx
+++ b/Сборочные отчёты/Сборочный отчёт_2025-06-14.xlsx
@@ -480,11 +480,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +502,18 @@
           <t>0099</t>
         </is>
       </c>
+      <c r="C1" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -510,6 +526,18 @@
           <t>0099</t>
         </is>
       </c>
+      <c r="C2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -522,6 +550,18 @@
           <t>447.984</t>
         </is>
       </c>
+      <c r="C3" s="5" t="n">
+        <v>-659.773</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>105.395</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1026.266</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>-201.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -534,6 +574,18 @@
           <t>9.484</t>
         </is>
       </c>
+      <c r="C4" s="5" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.316</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8.975</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -546,6 +598,18 @@
           <t>237</t>
         </is>
       </c>
+      <c r="C5" s="5" t="n">
+        <v>303</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>279</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -558,6 +622,18 @@
           <t>415</t>
         </is>
       </c>
+      <c r="C6" s="5" t="n">
+        <v>455</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>415</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>374</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>441</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -570,6 +646,18 @@
           <t>552</t>
         </is>
       </c>
+      <c r="C7" s="5" t="n">
+        <v>572</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>519</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>566</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -582,6 +670,18 @@
           <t>606</t>
         </is>
       </c>
+      <c r="C8" s="5" t="n">
+        <v>618</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>590</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>576</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>615</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -594,6 +694,18 @@
           <t>621</t>
         </is>
       </c>
+      <c r="C9" s="5" t="n">
+        <v>631</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>604</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>592</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>629</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -606,6 +718,18 @@
           <t>790</t>
         </is>
       </c>
+      <c r="C10" s="5" t="n">
+        <v>775</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>759</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>782</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -618,6 +742,18 @@
           <t>0.569</t>
         </is>
       </c>
+      <c r="C11" s="5" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.663</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -630,6 +766,18 @@
           <t>3.290</t>
         </is>
       </c>
+      <c r="C12" s="5" t="n">
+        <v>3.196</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.244</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4.153</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.242</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -642,6 +790,18 @@
           <t>525.000</t>
         </is>
       </c>
+      <c r="C13" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>513</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>526</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>531</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -654,6 +814,18 @@
           <t>5.000</t>
         </is>
       </c>
+      <c r="C14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -666,6 +838,18 @@
           <t>200.000</t>
         </is>
       </c>
+      <c r="C15" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -678,6 +862,18 @@
           <t>3.833</t>
         </is>
       </c>
+      <c r="C16" s="5" t="n">
+        <v>3.791</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.706</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -690,6 +886,18 @@
           <t>-67.227</t>
         </is>
       </c>
+      <c r="C17" s="5" t="n">
+        <v>-24.894</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-32.612</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-42.564</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-38.417</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -702,6 +910,18 @@
           <t>10.168</t>
         </is>
       </c>
+      <c r="C18" s="5" t="n">
+        <v>9.545999999999999</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.952</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.952</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.744999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -714,6 +934,18 @@
           <t>0.112</t>
         </is>
       </c>
+      <c r="C19" s="6" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.287</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -726,6 +958,18 @@
           <t>0.152</t>
         </is>
       </c>
+      <c r="C20" s="5" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.185</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -738,6 +982,18 @@
           <t>Отсутствует</t>
         </is>
       </c>
+      <c r="C21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -750,6 +1006,18 @@
           <t>Отсутствует</t>
         </is>
       </c>
+      <c r="C22" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -762,6 +1030,18 @@
           <t>Отсутствует</t>
         </is>
       </c>
+      <c r="C23" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -774,6 +1054,18 @@
           <t>Отсутствует</t>
         </is>
       </c>
+      <c r="C24" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -786,6 +1078,18 @@
           <t>Отсутствует</t>
         </is>
       </c>
+      <c r="C25" s="5" t="n">
+        <v>333</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>337</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>349</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -797,6 +1101,18 @@
         <is>
           <t>Отсутствует</t>
         </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>558</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
